--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.60191344673874</v>
+        <v>4.810310935095045</v>
       </c>
       <c r="D2" t="n">
-        <v>29.35020712457156</v>
+        <v>4.769408657742879</v>
       </c>
       <c r="E2" t="n">
-        <v>10.03069357745709</v>
+        <v>1.629987706336776</v>
       </c>
       <c r="F2" t="n">
-        <v>8.942375076834617</v>
+        <v>1.453135949985625</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.5357412999534</v>
+        <v>3.174557961242427</v>
       </c>
       <c r="D3" t="n">
-        <v>18.47553014628592</v>
+        <v>3.002273648771463</v>
       </c>
       <c r="E3" t="n">
-        <v>10.03069357745709</v>
+        <v>1.629987706336776</v>
       </c>
       <c r="F3" t="n">
-        <v>8.942375076834617</v>
+        <v>1.453135949985625</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.80626618223513</v>
+        <v>6.793518254613209</v>
       </c>
       <c r="D4" t="n">
-        <v>41.16655757435291</v>
+        <v>6.689565605832349</v>
       </c>
       <c r="E4" t="n">
-        <v>10.03069357745709</v>
+        <v>1.629987706336776</v>
       </c>
       <c r="F4" t="n">
-        <v>8.942375076834617</v>
+        <v>1.453135949985625</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.54658192546256</v>
+        <v>5.613819562887667</v>
       </c>
       <c r="D5" t="n">
-        <v>25.46269360126887</v>
+        <v>4.137687710206191</v>
       </c>
       <c r="E5" t="n">
-        <v>10.03069357745709</v>
+        <v>1.629987706336776</v>
       </c>
       <c r="F5" t="n">
-        <v>8.942375076834617</v>
+        <v>1.453135949985625</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.11159291468283</v>
+        <v>4.24313384863596</v>
       </c>
       <c r="D6" t="n">
-        <v>17.99039524267475</v>
+        <v>2.923439226934648</v>
       </c>
       <c r="E6" t="n">
-        <v>10.03069357745709</v>
+        <v>1.629987706336776</v>
       </c>
       <c r="F6" t="n">
-        <v>8.942375076834617</v>
+        <v>1.453135949985625</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.91229101162982</v>
+        <v>3.073247289389846</v>
       </c>
       <c r="D7" t="n">
-        <v>18.90920814402021</v>
+        <v>3.072746323403284</v>
       </c>
       <c r="E7" t="n">
-        <v>10.03069357745709</v>
+        <v>1.629987706336776</v>
       </c>
       <c r="F7" t="n">
-        <v>8.942375076834617</v>
+        <v>1.453135949985625</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>11.66304378680416</v>
+        <v>1.895244615355676</v>
       </c>
       <c r="D8" t="n">
-        <v>11.46826424430795</v>
+        <v>1.863592939700041</v>
       </c>
       <c r="E8" t="n">
-        <v>10.03069357745709</v>
+        <v>1.629987706336776</v>
       </c>
       <c r="F8" t="n">
-        <v>8.942375076834617</v>
+        <v>1.453135949985625</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>9.682499523222711</v>
+        <v>1.573406172523691</v>
       </c>
       <c r="D9" t="n">
-        <v>9.687661630111549</v>
+        <v>1.574245014893127</v>
       </c>
       <c r="E9" t="n">
-        <v>10.03069357745709</v>
+        <v>1.629987706336776</v>
       </c>
       <c r="F9" t="n">
-        <v>8.942375076834617</v>
+        <v>1.453135949985625</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>20.29579301344606</v>
+        <v>3.298066364684985</v>
       </c>
       <c r="D10" t="n">
-        <v>21.8456598943061</v>
+        <v>3.54991973282474</v>
       </c>
       <c r="E10" t="n">
-        <v>10.03069357745709</v>
+        <v>1.629987706336776</v>
       </c>
       <c r="F10" t="n">
-        <v>8.942375076834617</v>
+        <v>1.453135949985625</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>11.69713231403481</v>
+        <v>1.900784001030656</v>
       </c>
       <c r="D11" t="n">
-        <v>30.23460761995508</v>
+        <v>4.913123738242701</v>
       </c>
       <c r="E11" t="n">
-        <v>10.03069357745709</v>
+        <v>1.629987706336776</v>
       </c>
       <c r="F11" t="n">
-        <v>8.942375076834617</v>
+        <v>1.453135949985625</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
